--- a/xls/square_un_16_tri3_25.xlsx
+++ b/xls/square_un_16_tri3_25.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>861</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>340</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>741</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>4164</v>
+      </c>
+      <c r="I23">
+        <v>-2.1149661578487509e-7</v>
+      </c>
+      <c r="J23">
+        <v>-0.00038360845541195605</v>
+      </c>
+      <c r="K23">
+        <v>2.709507370196794</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>861</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>340</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>797</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24">
+        <v>4488</v>
+      </c>
+      <c r="I24">
+        <v>-1.1231560003288824e-7</v>
+      </c>
+      <c r="J24">
+        <v>-0.00019588359242643193</v>
+      </c>
+      <c r="K24">
+        <v>2.5721129204233684</v>
+      </c>
+    </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
         <v>11</v>
       </c>
       <c r="B25">
-        <v>790</v>
+        <v>861</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-1.7028407437394313</v>
+        <v>-7.572165252560032e-8</v>
       </c>
       <c r="J25">
-        <v>-1.2891128483629608</v>
+        <v>-0.00012954503817471478</v>
       </c>
       <c r="K25">
-        <v>2.234421137287309</v>
+        <v>2.4860265542459086</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>790</v>
+        <v>861</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-0.25639283242493455</v>
+        <v>-3.68799758658634e-8</v>
       </c>
       <c r="J26">
-        <v>-0.23459981829655796</v>
+        <v>-6.378925162216848e-5</v>
       </c>
       <c r="K26">
-        <v>3.680756822074087</v>
+        <v>2.3337393961522594</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>790</v>
+        <v>861</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-0.00969113293188719</v>
+        <v>-2.2920774552181236e-8</v>
       </c>
       <c r="J27">
-        <v>-0.009022910295669</v>
+        <v>-4.169834874615245e-5</v>
       </c>
       <c r="K27">
-        <v>3.3826635118445214</v>
+        <v>2.2509596182264193</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>790</v>
+        <v>861</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-0.0011234026320193632</v>
+        <v>-2.7386023761312603e-8</v>
       </c>
       <c r="J28">
-        <v>-0.0013054514699306667</v>
+        <v>-5.167847395147937e-5</v>
       </c>
       <c r="K28">
-        <v>3.031738036628439</v>
+        <v>2.300316856555262</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>790</v>
+        <v>861</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-0.0011256542745303676</v>
+        <v>-1.612644341164269e-8</v>
       </c>
       <c r="J29">
-        <v>-0.0011594473570174628</v>
+        <v>-2.9012824723278927e-5</v>
       </c>
       <c r="K29">
-        <v>2.987029682037846</v>
+        <v>2.171250167243428</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>790</v>
+        <v>861</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-0.00036730420357781557</v>
+        <v>-1.0833166610192877e-8</v>
       </c>
       <c r="J30">
-        <v>-0.0004012761410233876</v>
+        <v>-2.009355958076212e-5</v>
       </c>
       <c r="K30">
-        <v>2.768911102525037</v>
+        <v>2.0943907593385696</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>790</v>
+        <v>861</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-0.0002987926345571545</v>
+        <v>-9.516907225285993e-9</v>
       </c>
       <c r="J31">
-        <v>-0.00032731721931714657</v>
+        <v>-1.6893526848723142e-5</v>
       </c>
       <c r="K31">
-        <v>2.7237856704413135</v>
+        <v>2.052561152177701</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>790</v>
+        <v>861</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-0.00017634716659770567</v>
+        <v>-7.334647674938641e-9</v>
       </c>
       <c r="J32">
-        <v>-0.00020523029346878138</v>
+        <v>-1.3681264959024627e-5</v>
       </c>
       <c r="K32">
-        <v>2.6375575985298014</v>
+        <v>2.0123147665462073</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_25.xlsx
+++ b/xls/square_un_16_tri3_25.xlsx
@@ -482,13 +482,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-2.1149661578487509e-7</v>
+        <v>-0.12252940145839643</v>
       </c>
       <c r="J23">
-        <v>-0.00038360845541195605</v>
+        <v>-0.09548865261728325</v>
       </c>
       <c r="K23">
-        <v>2.709507370196794</v>
+        <v>3.1604216076871863</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -517,13 +517,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-1.1231560003288824e-7</v>
+        <v>-0.00022527011717382</v>
       </c>
       <c r="J24">
-        <v>-0.00019588359242643193</v>
+        <v>-0.00031901282083586117</v>
       </c>
       <c r="K24">
-        <v>2.5721129204233684</v>
+        <v>2.7604676212974195</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -552,13 +552,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-7.572165252560032e-8</v>
+        <v>-0.00022145604927821115</v>
       </c>
       <c r="J25">
-        <v>-0.00012954503817471478</v>
+        <v>-0.000199021767907618</v>
       </c>
       <c r="K25">
-        <v>2.4860265542459086</v>
+        <v>2.5727284303309124</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -587,13 +587,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-3.68799758658634e-8</v>
+        <v>-6.048508391254962e-5</v>
       </c>
       <c r="J26">
-        <v>-6.378925162216848e-5</v>
+        <v>-6.635265811416724e-5</v>
       </c>
       <c r="K26">
-        <v>2.3337393961522594</v>
+        <v>2.3833079811324756</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -622,13 +622,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-2.2920774552181236e-8</v>
+        <v>-4.201214677458319e-5</v>
       </c>
       <c r="J27">
-        <v>-4.169834874615245e-5</v>
+        <v>-4.487681250859207e-5</v>
       </c>
       <c r="K27">
-        <v>2.2509596182264193</v>
+        <v>2.2911396508928754</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -657,13 +657,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-2.7386023761312603e-8</v>
+        <v>-5.955821077063687e-5</v>
       </c>
       <c r="J28">
-        <v>-5.167847395147937e-5</v>
+        <v>-5.820539047206573e-5</v>
       </c>
       <c r="K28">
-        <v>2.300316856555262</v>
+        <v>2.323833818583148</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -692,13 +692,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-1.612644341164269e-8</v>
+        <v>-3.403331762000071e-5</v>
       </c>
       <c r="J29">
-        <v>-2.9012824723278927e-5</v>
+        <v>-3.214107494323448e-5</v>
       </c>
       <c r="K29">
-        <v>2.171250167243428</v>
+        <v>2.1889005062187903</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -727,13 +727,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-1.0833166610192877e-8</v>
+        <v>-2.1857003824468663e-5</v>
       </c>
       <c r="J30">
-        <v>-2.009355958076212e-5</v>
+        <v>-2.1675296633105044e-5</v>
       </c>
       <c r="K30">
-        <v>2.0943907593385696</v>
+        <v>2.113611963762165</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -762,13 +762,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-9.516907225285993e-9</v>
+        <v>-1.62669076715767e-5</v>
       </c>
       <c r="J31">
-        <v>-1.6893526848723142e-5</v>
+        <v>-1.6594042398766973e-5</v>
       </c>
       <c r="K31">
-        <v>2.052561152177701</v>
+        <v>2.066671511732779</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -797,13 +797,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-7.334647674938641e-9</v>
+        <v>-1.3344871716340724e-5</v>
       </c>
       <c r="J32">
-        <v>-1.3681264959024627e-5</v>
+        <v>-1.3640284137891668e-5</v>
       </c>
       <c r="K32">
-        <v>2.0123147665462073</v>
+        <v>2.022526970604015</v>
       </c>
     </row>
   </sheetData>
